--- a/apps/api/templates/waybill-leg3.xlsx
+++ b/apps/api/templates/waybill-leg3.xlsx
@@ -1296,7 +1296,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr autoPageBreaks="0"/>
+    <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:CJ100"/>
   <sheetFormatPr defaultColWidth="10.44921875" defaultRowHeight="11.45" customHeight="1" x14ac:dyDescent="0.1"/>
@@ -6306,7 +6306,8 @@
     <mergeCell ref="A12:BE12"/>
     <mergeCell ref="BW12:CJ12"/>
   </mergeCells>
-  <pageMargins left="0.75" right="1" top="0.75" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="56" max="16383" man="1"/>
   </rowBreaks>

--- a/apps/api/templates/waybill-leg3.xlsx
+++ b/apps/api/templates/waybill-leg3.xlsx
@@ -2729,9 +2729,7 @@
       <c r="BV38" s="32"/>
     </row>
     <row r="39" spans="1:88" s="1" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A39" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="A39" s="1"/>
       <c r="Q39" s="33"/>
       <c r="R39" s="33"/>
       <c r="S39" s="33"/>
@@ -2741,11 +2739,7 @@
       <c r="W39" s="33"/>
       <c r="X39" s="33"/>
       <c r="Y39" s="33"/>
-      <c r="AA39" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{dispatcher_fio}}</t>
-        </is>
-      </c>
+      <c r="AA39" s="34"/>
       <c r="AB39" s="34"/>
       <c r="AC39" s="34"/>
       <c r="AD39" s="34"/>
@@ -2801,9 +2795,7 @@
       <c r="CJ39" s="37"/>
     </row>
     <row r="40" spans="1:88" s="1" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="Q40" s="16" t="s">
-        <v>34</v>
-      </c>
+      <c r="Q40" s="16"/>
       <c r="R40" s="16"/>
       <c r="S40" s="16"/>
       <c r="T40" s="16"/>
@@ -2812,9 +2804,7 @@
       <c r="W40" s="16"/>
       <c r="X40" s="16"/>
       <c r="Y40" s="16"/>
-      <c r="AA40" s="16" t="s">
-        <v>35</v>
-      </c>
+      <c r="AA40" s="16"/>
       <c r="AB40" s="16"/>
       <c r="AC40" s="16"/>
       <c r="AD40" s="16"/>

--- a/apps/api/templates/waybill-leg3.xlsx
+++ b/apps/api/templates/waybill-leg3.xlsx
@@ -2489,6 +2489,11 @@
       <c r="N31" s="11"/>
       <c r="O31" s="11"/>
       <c r="P31" s="11"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{communication_kind}}</t>
+        </is>
+      </c>
     </row>
     <row r="32" spans="1:88" s="1" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.1">
       <c r="BB32" s="11" t="s">
@@ -3874,7 +3879,11 @@
       <c r="E61" s="71"/>
       <c r="F61" s="71"/>
       <c r="G61" s="71"/>
-      <c r="H61" s="56"/>
+      <c r="H61" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task_from}}</t>
+        </is>
+      </c>
       <c r="I61" s="56"/>
       <c r="J61" s="56"/>
       <c r="K61" s="56"/>
@@ -3894,7 +3903,11 @@
       <c r="Y61" s="56"/>
       <c r="Z61" s="56"/>
       <c r="AA61" s="56"/>
-      <c r="AB61" s="74"/>
+      <c r="AB61" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task_to}}</t>
+        </is>
+      </c>
       <c r="AC61" s="74"/>
       <c r="AD61" s="74"/>
       <c r="AE61" s="74"/>
@@ -3913,19 +3926,31 @@
       <c r="AR61" s="74"/>
       <c r="AS61" s="74"/>
       <c r="AT61" s="74"/>
-      <c r="AU61" s="30"/>
+      <c r="AU61" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task_departure_hh}}</t>
+        </is>
+      </c>
       <c r="AV61" s="30"/>
       <c r="AW61" s="30"/>
       <c r="AX61" s="30"/>
       <c r="AY61" s="30"/>
       <c r="AZ61" s="30"/>
-      <c r="BA61" s="30"/>
+      <c r="BA61" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task_departure_mm}}</t>
+        </is>
+      </c>
       <c r="BB61" s="30"/>
       <c r="BC61" s="30"/>
       <c r="BD61" s="30"/>
       <c r="BE61" s="30"/>
       <c r="BF61" s="30"/>
-      <c r="BG61" s="75"/>
+      <c r="BG61" s="75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task_cargo}}</t>
+        </is>
+      </c>
       <c r="BH61" s="75"/>
       <c r="BI61" s="75"/>
       <c r="BJ61" s="75"/>
@@ -3943,7 +3968,11 @@
       <c r="BV61" s="75"/>
       <c r="BW61" s="75"/>
       <c r="BX61" s="75"/>
-      <c r="BY61" s="78"/>
+      <c r="BY61" s="78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{customer_name}}</t>
+        </is>
+      </c>
       <c r="BZ61" s="78"/>
       <c r="CA61" s="78"/>
       <c r="CB61" s="78"/>
@@ -4056,7 +4085,11 @@
       <c r="E63" s="71"/>
       <c r="F63" s="71"/>
       <c r="G63" s="71"/>
-      <c r="H63" s="80"/>
+      <c r="H63" s="80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task2_from}}</t>
+        </is>
+      </c>
       <c r="I63" s="80"/>
       <c r="J63" s="80"/>
       <c r="K63" s="80"/>
@@ -4076,7 +4109,11 @@
       <c r="Y63" s="80"/>
       <c r="Z63" s="80"/>
       <c r="AA63" s="80"/>
-      <c r="AB63" s="59"/>
+      <c r="AB63" s="59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task2_to}}</t>
+        </is>
+      </c>
       <c r="AC63" s="59"/>
       <c r="AD63" s="59"/>
       <c r="AE63" s="59"/>
@@ -4107,7 +4144,11 @@
       <c r="BD63" s="30"/>
       <c r="BE63" s="30"/>
       <c r="BF63" s="30"/>
-      <c r="BG63" s="75"/>
+      <c r="BG63" s="75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task2_cargo}}</t>
+        </is>
+      </c>
       <c r="BH63" s="75"/>
       <c r="BI63" s="75"/>
       <c r="BJ63" s="75"/>
@@ -4125,7 +4166,11 @@
       <c r="BV63" s="75"/>
       <c r="BW63" s="75"/>
       <c r="BX63" s="75"/>
-      <c r="BY63" s="78"/>
+      <c r="BY63" s="78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task2_customer}}</t>
+        </is>
+      </c>
       <c r="BZ63" s="78"/>
       <c r="CA63" s="78"/>
       <c r="CB63" s="78"/>
@@ -4238,7 +4283,11 @@
       <c r="E65" s="71"/>
       <c r="F65" s="71"/>
       <c r="G65" s="71"/>
-      <c r="H65" s="80"/>
+      <c r="H65" s="80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task3_from}}</t>
+        </is>
+      </c>
       <c r="I65" s="80"/>
       <c r="J65" s="80"/>
       <c r="K65" s="80"/>
@@ -4258,7 +4307,11 @@
       <c r="Y65" s="80"/>
       <c r="Z65" s="80"/>
       <c r="AA65" s="80"/>
-      <c r="AB65" s="59"/>
+      <c r="AB65" s="59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task3_to}}</t>
+        </is>
+      </c>
       <c r="AC65" s="59"/>
       <c r="AD65" s="59"/>
       <c r="AE65" s="59"/>
@@ -4289,7 +4342,11 @@
       <c r="BD65" s="30"/>
       <c r="BE65" s="30"/>
       <c r="BF65" s="30"/>
-      <c r="BG65" s="75"/>
+      <c r="BG65" s="75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task3_cargo}}</t>
+        </is>
+      </c>
       <c r="BH65" s="75"/>
       <c r="BI65" s="75"/>
       <c r="BJ65" s="75"/>
@@ -4307,7 +4364,11 @@
       <c r="BV65" s="75"/>
       <c r="BW65" s="75"/>
       <c r="BX65" s="75"/>
-      <c r="BY65" s="78"/>
+      <c r="BY65" s="78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task3_customer}}</t>
+        </is>
+      </c>
       <c r="BZ65" s="78"/>
       <c r="CA65" s="78"/>
       <c r="CB65" s="78"/>
@@ -4420,7 +4481,11 @@
       <c r="E67" s="71"/>
       <c r="F67" s="71"/>
       <c r="G67" s="71"/>
-      <c r="H67" s="80"/>
+      <c r="H67" s="80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task4_from}}</t>
+        </is>
+      </c>
       <c r="I67" s="80"/>
       <c r="J67" s="80"/>
       <c r="K67" s="80"/>
@@ -4440,7 +4505,11 @@
       <c r="Y67" s="80"/>
       <c r="Z67" s="80"/>
       <c r="AA67" s="80"/>
-      <c r="AB67" s="59"/>
+      <c r="AB67" s="59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task4_to}}</t>
+        </is>
+      </c>
       <c r="AC67" s="59"/>
       <c r="AD67" s="59"/>
       <c r="AE67" s="59"/>
@@ -4471,7 +4540,11 @@
       <c r="BD67" s="30"/>
       <c r="BE67" s="30"/>
       <c r="BF67" s="30"/>
-      <c r="BG67" s="75"/>
+      <c r="BG67" s="75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task4_cargo}}</t>
+        </is>
+      </c>
       <c r="BH67" s="75"/>
       <c r="BI67" s="75"/>
       <c r="BJ67" s="75"/>
@@ -4489,7 +4562,11 @@
       <c r="BV67" s="75"/>
       <c r="BW67" s="75"/>
       <c r="BX67" s="75"/>
-      <c r="BY67" s="78"/>
+      <c r="BY67" s="78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task4_customer}}</t>
+        </is>
+      </c>
       <c r="BZ67" s="78"/>
       <c r="CA67" s="78"/>
       <c r="CB67" s="78"/>

--- a/apps/api/templates/waybill-leg3.xlsx
+++ b/apps/api/templates/waybill-leg3.xlsx
@@ -957,54 +957,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Имя " descr="Descr ">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6378,6 +6330,5 @@
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="56" max="16383" man="1"/>
   </rowBreaks>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/apps/api/templates/waybill-leg3.xlsx
+++ b/apps/api/templates/waybill-leg3.xlsx
@@ -4631,7 +4631,11 @@
       <c r="E69" s="71"/>
       <c r="F69" s="71"/>
       <c r="G69" s="71"/>
-      <c r="H69" s="80"/>
+      <c r="H69" s="80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task5_from}}</t>
+        </is>
+      </c>
       <c r="I69" s="80"/>
       <c r="J69" s="80"/>
       <c r="K69" s="80"/>
@@ -4651,7 +4655,11 @@
       <c r="Y69" s="80"/>
       <c r="Z69" s="80"/>
       <c r="AA69" s="80"/>
-      <c r="AB69" s="59"/>
+      <c r="AB69" s="59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task5_to}}</t>
+        </is>
+      </c>
       <c r="AC69" s="59"/>
       <c r="AD69" s="59"/>
       <c r="AE69" s="59"/>
@@ -4682,7 +4690,11 @@
       <c r="BD69" s="30"/>
       <c r="BE69" s="30"/>
       <c r="BF69" s="30"/>
-      <c r="BG69" s="75"/>
+      <c r="BG69" s="75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task5_cargo}}</t>
+        </is>
+      </c>
       <c r="BH69" s="75"/>
       <c r="BI69" s="75"/>
       <c r="BJ69" s="75"/>
@@ -4700,7 +4712,11 @@
       <c r="BV69" s="75"/>
       <c r="BW69" s="75"/>
       <c r="BX69" s="75"/>
-      <c r="BY69" s="78"/>
+      <c r="BY69" s="78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task5_customer}}</t>
+        </is>
+      </c>
       <c r="BZ69" s="78"/>
       <c r="CA69" s="78"/>
       <c r="CB69" s="78"/>
@@ -4813,7 +4829,11 @@
       <c r="E71" s="71"/>
       <c r="F71" s="71"/>
       <c r="G71" s="71"/>
-      <c r="H71" s="80"/>
+      <c r="H71" s="80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task6_from}}</t>
+        </is>
+      </c>
       <c r="I71" s="80"/>
       <c r="J71" s="80"/>
       <c r="K71" s="80"/>
@@ -4833,7 +4853,11 @@
       <c r="Y71" s="80"/>
       <c r="Z71" s="80"/>
       <c r="AA71" s="80"/>
-      <c r="AB71" s="59"/>
+      <c r="AB71" s="59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task6_to}}</t>
+        </is>
+      </c>
       <c r="AC71" s="59"/>
       <c r="AD71" s="59"/>
       <c r="AE71" s="59"/>
@@ -4864,7 +4888,11 @@
       <c r="BD71" s="30"/>
       <c r="BE71" s="30"/>
       <c r="BF71" s="30"/>
-      <c r="BG71" s="75"/>
+      <c r="BG71" s="75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task6_cargo}}</t>
+        </is>
+      </c>
       <c r="BH71" s="75"/>
       <c r="BI71" s="75"/>
       <c r="BJ71" s="75"/>
@@ -4882,7 +4910,11 @@
       <c r="BV71" s="75"/>
       <c r="BW71" s="75"/>
       <c r="BX71" s="75"/>
-      <c r="BY71" s="78"/>
+      <c r="BY71" s="78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task6_customer}}</t>
+        </is>
+      </c>
       <c r="BZ71" s="78"/>
       <c r="CA71" s="78"/>
       <c r="CB71" s="78"/>
@@ -4995,7 +5027,11 @@
       <c r="E73" s="71"/>
       <c r="F73" s="71"/>
       <c r="G73" s="71"/>
-      <c r="H73" s="80"/>
+      <c r="H73" s="80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task7_from}}</t>
+        </is>
+      </c>
       <c r="I73" s="80"/>
       <c r="J73" s="80"/>
       <c r="K73" s="80"/>
@@ -5015,7 +5051,11 @@
       <c r="Y73" s="80"/>
       <c r="Z73" s="80"/>
       <c r="AA73" s="80"/>
-      <c r="AB73" s="59"/>
+      <c r="AB73" s="59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task7_to}}</t>
+        </is>
+      </c>
       <c r="AC73" s="59"/>
       <c r="AD73" s="59"/>
       <c r="AE73" s="59"/>
@@ -5046,7 +5086,11 @@
       <c r="BD73" s="30"/>
       <c r="BE73" s="30"/>
       <c r="BF73" s="30"/>
-      <c r="BG73" s="75"/>
+      <c r="BG73" s="75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task7_cargo}}</t>
+        </is>
+      </c>
       <c r="BH73" s="75"/>
       <c r="BI73" s="75"/>
       <c r="BJ73" s="75"/>
@@ -5064,7 +5108,11 @@
       <c r="BV73" s="75"/>
       <c r="BW73" s="75"/>
       <c r="BX73" s="75"/>
-      <c r="BY73" s="78"/>
+      <c r="BY73" s="78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task7_customer}}</t>
+        </is>
+      </c>
       <c r="BZ73" s="78"/>
       <c r="CA73" s="78"/>
       <c r="CB73" s="78"/>
@@ -5177,7 +5225,11 @@
       <c r="E75" s="71"/>
       <c r="F75" s="71"/>
       <c r="G75" s="71"/>
-      <c r="H75" s="80"/>
+      <c r="H75" s="80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task8_from}}</t>
+        </is>
+      </c>
       <c r="I75" s="80"/>
       <c r="J75" s="80"/>
       <c r="K75" s="80"/>
@@ -5197,7 +5249,11 @@
       <c r="Y75" s="80"/>
       <c r="Z75" s="80"/>
       <c r="AA75" s="80"/>
-      <c r="AB75" s="59"/>
+      <c r="AB75" s="59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task8_to}}</t>
+        </is>
+      </c>
       <c r="AC75" s="59"/>
       <c r="AD75" s="59"/>
       <c r="AE75" s="59"/>
@@ -5228,7 +5284,11 @@
       <c r="BD75" s="30"/>
       <c r="BE75" s="30"/>
       <c r="BF75" s="30"/>
-      <c r="BG75" s="75"/>
+      <c r="BG75" s="75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task8_cargo}}</t>
+        </is>
+      </c>
       <c r="BH75" s="75"/>
       <c r="BI75" s="75"/>
       <c r="BJ75" s="75"/>
@@ -5246,7 +5306,11 @@
       <c r="BV75" s="75"/>
       <c r="BW75" s="75"/>
       <c r="BX75" s="75"/>
-      <c r="BY75" s="78"/>
+      <c r="BY75" s="78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task8_customer}}</t>
+        </is>
+      </c>
       <c r="BZ75" s="78"/>
       <c r="CA75" s="78"/>
       <c r="CB75" s="78"/>
@@ -5359,7 +5423,11 @@
       <c r="E77" s="71"/>
       <c r="F77" s="71"/>
       <c r="G77" s="71"/>
-      <c r="H77" s="80"/>
+      <c r="H77" s="80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task9_from}}</t>
+        </is>
+      </c>
       <c r="I77" s="80"/>
       <c r="J77" s="80"/>
       <c r="K77" s="80"/>
@@ -5379,7 +5447,11 @@
       <c r="Y77" s="80"/>
       <c r="Z77" s="80"/>
       <c r="AA77" s="80"/>
-      <c r="AB77" s="59"/>
+      <c r="AB77" s="59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task9_to}}</t>
+        </is>
+      </c>
       <c r="AC77" s="59"/>
       <c r="AD77" s="59"/>
       <c r="AE77" s="59"/>
@@ -5410,7 +5482,11 @@
       <c r="BD77" s="30"/>
       <c r="BE77" s="30"/>
       <c r="BF77" s="30"/>
-      <c r="BG77" s="75"/>
+      <c r="BG77" s="75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task9_cargo}}</t>
+        </is>
+      </c>
       <c r="BH77" s="75"/>
       <c r="BI77" s="75"/>
       <c r="BJ77" s="75"/>
@@ -5428,7 +5504,11 @@
       <c r="BV77" s="75"/>
       <c r="BW77" s="75"/>
       <c r="BX77" s="75"/>
-      <c r="BY77" s="78"/>
+      <c r="BY77" s="78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task9_customer}}</t>
+        </is>
+      </c>
       <c r="BZ77" s="78"/>
       <c r="CA77" s="78"/>
       <c r="CB77" s="78"/>
@@ -5541,7 +5621,11 @@
       <c r="E79" s="71"/>
       <c r="F79" s="71"/>
       <c r="G79" s="71"/>
-      <c r="H79" s="80"/>
+      <c r="H79" s="80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task10_from}}</t>
+        </is>
+      </c>
       <c r="I79" s="80"/>
       <c r="J79" s="80"/>
       <c r="K79" s="80"/>
@@ -5561,7 +5645,11 @@
       <c r="Y79" s="80"/>
       <c r="Z79" s="80"/>
       <c r="AA79" s="80"/>
-      <c r="AB79" s="59"/>
+      <c r="AB79" s="59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task10_to}}</t>
+        </is>
+      </c>
       <c r="AC79" s="59"/>
       <c r="AD79" s="59"/>
       <c r="AE79" s="59"/>
@@ -5592,7 +5680,11 @@
       <c r="BD79" s="30"/>
       <c r="BE79" s="30"/>
       <c r="BF79" s="30"/>
-      <c r="BG79" s="75"/>
+      <c r="BG79" s="75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task10_cargo}}</t>
+        </is>
+      </c>
       <c r="BH79" s="75"/>
       <c r="BI79" s="75"/>
       <c r="BJ79" s="75"/>
@@ -5610,7 +5702,11 @@
       <c r="BV79" s="75"/>
       <c r="BW79" s="75"/>
       <c r="BX79" s="75"/>
-      <c r="BY79" s="78"/>
+      <c r="BY79" s="78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task10_customer}}</t>
+        </is>
+      </c>
       <c r="BZ79" s="78"/>
       <c r="CA79" s="78"/>
       <c r="CB79" s="78"/>

--- a/apps/api/templates/waybill-leg3.xlsx
+++ b/apps/api/templates/waybill-leg3.xlsx
@@ -2244,11 +2244,7 @@
       <c r="K27" s="11"/>
       <c r="L27" s="11"/>
       <c r="M27" s="11"/>
-      <c r="N27" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{customer_name}}, {{customer_address}}</t>
-        </is>
-      </c>
+      <c r="N27" s="28"/>
       <c r="O27" s="28"/>
       <c r="P27" s="28"/>
       <c r="Q27" s="28"/>
@@ -3831,11 +3827,7 @@
       <c r="E61" s="71"/>
       <c r="F61" s="71"/>
       <c r="G61" s="71"/>
-      <c r="H61" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task_from}}</t>
-        </is>
-      </c>
+      <c r="H61" s="56"/>
       <c r="I61" s="56"/>
       <c r="J61" s="56"/>
       <c r="K61" s="56"/>
@@ -3855,11 +3847,7 @@
       <c r="Y61" s="56"/>
       <c r="Z61" s="56"/>
       <c r="AA61" s="56"/>
-      <c r="AB61" s="74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task_to}}</t>
-        </is>
-      </c>
+      <c r="AB61" s="74"/>
       <c r="AC61" s="74"/>
       <c r="AD61" s="74"/>
       <c r="AE61" s="74"/>
@@ -3878,31 +3866,19 @@
       <c r="AR61" s="74"/>
       <c r="AS61" s="74"/>
       <c r="AT61" s="74"/>
-      <c r="AU61" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task_departure_hh}}</t>
-        </is>
-      </c>
+      <c r="AU61" s="30"/>
       <c r="AV61" s="30"/>
       <c r="AW61" s="30"/>
       <c r="AX61" s="30"/>
       <c r="AY61" s="30"/>
       <c r="AZ61" s="30"/>
-      <c r="BA61" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task_departure_mm}}</t>
-        </is>
-      </c>
+      <c r="BA61" s="30"/>
       <c r="BB61" s="30"/>
       <c r="BC61" s="30"/>
       <c r="BD61" s="30"/>
       <c r="BE61" s="30"/>
       <c r="BF61" s="30"/>
-      <c r="BG61" s="75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task_cargo}}</t>
-        </is>
-      </c>
+      <c r="BG61" s="75"/>
       <c r="BH61" s="75"/>
       <c r="BI61" s="75"/>
       <c r="BJ61" s="75"/>
@@ -3920,11 +3896,7 @@
       <c r="BV61" s="75"/>
       <c r="BW61" s="75"/>
       <c r="BX61" s="75"/>
-      <c r="BY61" s="78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{customer_name}}</t>
-        </is>
-      </c>
+      <c r="BY61" s="78"/>
       <c r="BZ61" s="78"/>
       <c r="CA61" s="78"/>
       <c r="CB61" s="78"/>
@@ -4037,11 +4009,7 @@
       <c r="E63" s="71"/>
       <c r="F63" s="71"/>
       <c r="G63" s="71"/>
-      <c r="H63" s="80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task2_from}}</t>
-        </is>
-      </c>
+      <c r="H63" s="80"/>
       <c r="I63" s="80"/>
       <c r="J63" s="80"/>
       <c r="K63" s="80"/>
@@ -4061,11 +4029,7 @@
       <c r="Y63" s="80"/>
       <c r="Z63" s="80"/>
       <c r="AA63" s="80"/>
-      <c r="AB63" s="59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task2_to}}</t>
-        </is>
-      </c>
+      <c r="AB63" s="59"/>
       <c r="AC63" s="59"/>
       <c r="AD63" s="59"/>
       <c r="AE63" s="59"/>
@@ -4096,11 +4060,7 @@
       <c r="BD63" s="30"/>
       <c r="BE63" s="30"/>
       <c r="BF63" s="30"/>
-      <c r="BG63" s="75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task2_cargo}}</t>
-        </is>
-      </c>
+      <c r="BG63" s="75"/>
       <c r="BH63" s="75"/>
       <c r="BI63" s="75"/>
       <c r="BJ63" s="75"/>
@@ -4118,11 +4078,7 @@
       <c r="BV63" s="75"/>
       <c r="BW63" s="75"/>
       <c r="BX63" s="75"/>
-      <c r="BY63" s="78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task2_customer}}</t>
-        </is>
-      </c>
+      <c r="BY63" s="78"/>
       <c r="BZ63" s="78"/>
       <c r="CA63" s="78"/>
       <c r="CB63" s="78"/>
@@ -4235,11 +4191,7 @@
       <c r="E65" s="71"/>
       <c r="F65" s="71"/>
       <c r="G65" s="71"/>
-      <c r="H65" s="80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task3_from}}</t>
-        </is>
-      </c>
+      <c r="H65" s="80"/>
       <c r="I65" s="80"/>
       <c r="J65" s="80"/>
       <c r="K65" s="80"/>
@@ -4259,11 +4211,7 @@
       <c r="Y65" s="80"/>
       <c r="Z65" s="80"/>
       <c r="AA65" s="80"/>
-      <c r="AB65" s="59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task3_to}}</t>
-        </is>
-      </c>
+      <c r="AB65" s="59"/>
       <c r="AC65" s="59"/>
       <c r="AD65" s="59"/>
       <c r="AE65" s="59"/>
@@ -4294,11 +4242,7 @@
       <c r="BD65" s="30"/>
       <c r="BE65" s="30"/>
       <c r="BF65" s="30"/>
-      <c r="BG65" s="75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task3_cargo}}</t>
-        </is>
-      </c>
+      <c r="BG65" s="75"/>
       <c r="BH65" s="75"/>
       <c r="BI65" s="75"/>
       <c r="BJ65" s="75"/>
@@ -4316,11 +4260,7 @@
       <c r="BV65" s="75"/>
       <c r="BW65" s="75"/>
       <c r="BX65" s="75"/>
-      <c r="BY65" s="78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task3_customer}}</t>
-        </is>
-      </c>
+      <c r="BY65" s="78"/>
       <c r="BZ65" s="78"/>
       <c r="CA65" s="78"/>
       <c r="CB65" s="78"/>
@@ -4433,11 +4373,7 @@
       <c r="E67" s="71"/>
       <c r="F67" s="71"/>
       <c r="G67" s="71"/>
-      <c r="H67" s="80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task4_from}}</t>
-        </is>
-      </c>
+      <c r="H67" s="80"/>
       <c r="I67" s="80"/>
       <c r="J67" s="80"/>
       <c r="K67" s="80"/>
@@ -4457,11 +4393,7 @@
       <c r="Y67" s="80"/>
       <c r="Z67" s="80"/>
       <c r="AA67" s="80"/>
-      <c r="AB67" s="59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task4_to}}</t>
-        </is>
-      </c>
+      <c r="AB67" s="59"/>
       <c r="AC67" s="59"/>
       <c r="AD67" s="59"/>
       <c r="AE67" s="59"/>
@@ -4492,11 +4424,7 @@
       <c r="BD67" s="30"/>
       <c r="BE67" s="30"/>
       <c r="BF67" s="30"/>
-      <c r="BG67" s="75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task4_cargo}}</t>
-        </is>
-      </c>
+      <c r="BG67" s="75"/>
       <c r="BH67" s="75"/>
       <c r="BI67" s="75"/>
       <c r="BJ67" s="75"/>
@@ -4514,11 +4442,7 @@
       <c r="BV67" s="75"/>
       <c r="BW67" s="75"/>
       <c r="BX67" s="75"/>
-      <c r="BY67" s="78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task4_customer}}</t>
-        </is>
-      </c>
+      <c r="BY67" s="78"/>
       <c r="BZ67" s="78"/>
       <c r="CA67" s="78"/>
       <c r="CB67" s="78"/>
@@ -4631,11 +4555,7 @@
       <c r="E69" s="71"/>
       <c r="F69" s="71"/>
       <c r="G69" s="71"/>
-      <c r="H69" s="80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task5_from}}</t>
-        </is>
-      </c>
+      <c r="H69" s="80"/>
       <c r="I69" s="80"/>
       <c r="J69" s="80"/>
       <c r="K69" s="80"/>
@@ -4655,11 +4575,7 @@
       <c r="Y69" s="80"/>
       <c r="Z69" s="80"/>
       <c r="AA69" s="80"/>
-      <c r="AB69" s="59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task5_to}}</t>
-        </is>
-      </c>
+      <c r="AB69" s="59"/>
       <c r="AC69" s="59"/>
       <c r="AD69" s="59"/>
       <c r="AE69" s="59"/>
@@ -4690,11 +4606,7 @@
       <c r="BD69" s="30"/>
       <c r="BE69" s="30"/>
       <c r="BF69" s="30"/>
-      <c r="BG69" s="75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task5_cargo}}</t>
-        </is>
-      </c>
+      <c r="BG69" s="75"/>
       <c r="BH69" s="75"/>
       <c r="BI69" s="75"/>
       <c r="BJ69" s="75"/>
@@ -4712,11 +4624,7 @@
       <c r="BV69" s="75"/>
       <c r="BW69" s="75"/>
       <c r="BX69" s="75"/>
-      <c r="BY69" s="78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task5_customer}}</t>
-        </is>
-      </c>
+      <c r="BY69" s="78"/>
       <c r="BZ69" s="78"/>
       <c r="CA69" s="78"/>
       <c r="CB69" s="78"/>
@@ -4829,11 +4737,7 @@
       <c r="E71" s="71"/>
       <c r="F71" s="71"/>
       <c r="G71" s="71"/>
-      <c r="H71" s="80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task6_from}}</t>
-        </is>
-      </c>
+      <c r="H71" s="80"/>
       <c r="I71" s="80"/>
       <c r="J71" s="80"/>
       <c r="K71" s="80"/>
@@ -4853,11 +4757,7 @@
       <c r="Y71" s="80"/>
       <c r="Z71" s="80"/>
       <c r="AA71" s="80"/>
-      <c r="AB71" s="59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task6_to}}</t>
-        </is>
-      </c>
+      <c r="AB71" s="59"/>
       <c r="AC71" s="59"/>
       <c r="AD71" s="59"/>
       <c r="AE71" s="59"/>
@@ -4888,11 +4788,7 @@
       <c r="BD71" s="30"/>
       <c r="BE71" s="30"/>
       <c r="BF71" s="30"/>
-      <c r="BG71" s="75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task6_cargo}}</t>
-        </is>
-      </c>
+      <c r="BG71" s="75"/>
       <c r="BH71" s="75"/>
       <c r="BI71" s="75"/>
       <c r="BJ71" s="75"/>
@@ -4910,11 +4806,7 @@
       <c r="BV71" s="75"/>
       <c r="BW71" s="75"/>
       <c r="BX71" s="75"/>
-      <c r="BY71" s="78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task6_customer}}</t>
-        </is>
-      </c>
+      <c r="BY71" s="78"/>
       <c r="BZ71" s="78"/>
       <c r="CA71" s="78"/>
       <c r="CB71" s="78"/>
@@ -5027,11 +4919,7 @@
       <c r="E73" s="71"/>
       <c r="F73" s="71"/>
       <c r="G73" s="71"/>
-      <c r="H73" s="80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task7_from}}</t>
-        </is>
-      </c>
+      <c r="H73" s="80"/>
       <c r="I73" s="80"/>
       <c r="J73" s="80"/>
       <c r="K73" s="80"/>
@@ -5051,11 +4939,7 @@
       <c r="Y73" s="80"/>
       <c r="Z73" s="80"/>
       <c r="AA73" s="80"/>
-      <c r="AB73" s="59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task7_to}}</t>
-        </is>
-      </c>
+      <c r="AB73" s="59"/>
       <c r="AC73" s="59"/>
       <c r="AD73" s="59"/>
       <c r="AE73" s="59"/>
@@ -5086,11 +4970,7 @@
       <c r="BD73" s="30"/>
       <c r="BE73" s="30"/>
       <c r="BF73" s="30"/>
-      <c r="BG73" s="75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task7_cargo}}</t>
-        </is>
-      </c>
+      <c r="BG73" s="75"/>
       <c r="BH73" s="75"/>
       <c r="BI73" s="75"/>
       <c r="BJ73" s="75"/>
@@ -5108,11 +4988,7 @@
       <c r="BV73" s="75"/>
       <c r="BW73" s="75"/>
       <c r="BX73" s="75"/>
-      <c r="BY73" s="78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task7_customer}}</t>
-        </is>
-      </c>
+      <c r="BY73" s="78"/>
       <c r="BZ73" s="78"/>
       <c r="CA73" s="78"/>
       <c r="CB73" s="78"/>
@@ -5225,11 +5101,7 @@
       <c r="E75" s="71"/>
       <c r="F75" s="71"/>
       <c r="G75" s="71"/>
-      <c r="H75" s="80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task8_from}}</t>
-        </is>
-      </c>
+      <c r="H75" s="80"/>
       <c r="I75" s="80"/>
       <c r="J75" s="80"/>
       <c r="K75" s="80"/>
@@ -5249,11 +5121,7 @@
       <c r="Y75" s="80"/>
       <c r="Z75" s="80"/>
       <c r="AA75" s="80"/>
-      <c r="AB75" s="59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task8_to}}</t>
-        </is>
-      </c>
+      <c r="AB75" s="59"/>
       <c r="AC75" s="59"/>
       <c r="AD75" s="59"/>
       <c r="AE75" s="59"/>
@@ -5284,11 +5152,7 @@
       <c r="BD75" s="30"/>
       <c r="BE75" s="30"/>
       <c r="BF75" s="30"/>
-      <c r="BG75" s="75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task8_cargo}}</t>
-        </is>
-      </c>
+      <c r="BG75" s="75"/>
       <c r="BH75" s="75"/>
       <c r="BI75" s="75"/>
       <c r="BJ75" s="75"/>
@@ -5306,11 +5170,7 @@
       <c r="BV75" s="75"/>
       <c r="BW75" s="75"/>
       <c r="BX75" s="75"/>
-      <c r="BY75" s="78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task8_customer}}</t>
-        </is>
-      </c>
+      <c r="BY75" s="78"/>
       <c r="BZ75" s="78"/>
       <c r="CA75" s="78"/>
       <c r="CB75" s="78"/>
@@ -5423,11 +5283,7 @@
       <c r="E77" s="71"/>
       <c r="F77" s="71"/>
       <c r="G77" s="71"/>
-      <c r="H77" s="80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task9_from}}</t>
-        </is>
-      </c>
+      <c r="H77" s="80"/>
       <c r="I77" s="80"/>
       <c r="J77" s="80"/>
       <c r="K77" s="80"/>
@@ -5447,11 +5303,7 @@
       <c r="Y77" s="80"/>
       <c r="Z77" s="80"/>
       <c r="AA77" s="80"/>
-      <c r="AB77" s="59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task9_to}}</t>
-        </is>
-      </c>
+      <c r="AB77" s="59"/>
       <c r="AC77" s="59"/>
       <c r="AD77" s="59"/>
       <c r="AE77" s="59"/>
@@ -5482,11 +5334,7 @@
       <c r="BD77" s="30"/>
       <c r="BE77" s="30"/>
       <c r="BF77" s="30"/>
-      <c r="BG77" s="75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task9_cargo}}</t>
-        </is>
-      </c>
+      <c r="BG77" s="75"/>
       <c r="BH77" s="75"/>
       <c r="BI77" s="75"/>
       <c r="BJ77" s="75"/>
@@ -5504,11 +5352,7 @@
       <c r="BV77" s="75"/>
       <c r="BW77" s="75"/>
       <c r="BX77" s="75"/>
-      <c r="BY77" s="78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task9_customer}}</t>
-        </is>
-      </c>
+      <c r="BY77" s="78"/>
       <c r="BZ77" s="78"/>
       <c r="CA77" s="78"/>
       <c r="CB77" s="78"/>
@@ -5621,11 +5465,7 @@
       <c r="E79" s="71"/>
       <c r="F79" s="71"/>
       <c r="G79" s="71"/>
-      <c r="H79" s="80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task10_from}}</t>
-        </is>
-      </c>
+      <c r="H79" s="80"/>
       <c r="I79" s="80"/>
       <c r="J79" s="80"/>
       <c r="K79" s="80"/>
@@ -5645,11 +5485,7 @@
       <c r="Y79" s="80"/>
       <c r="Z79" s="80"/>
       <c r="AA79" s="80"/>
-      <c r="AB79" s="59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task10_to}}</t>
-        </is>
-      </c>
+      <c r="AB79" s="59"/>
       <c r="AC79" s="59"/>
       <c r="AD79" s="59"/>
       <c r="AE79" s="59"/>
@@ -5680,11 +5516,7 @@
       <c r="BD79" s="30"/>
       <c r="BE79" s="30"/>
       <c r="BF79" s="30"/>
-      <c r="BG79" s="75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task10_cargo}}</t>
-        </is>
-      </c>
+      <c r="BG79" s="75"/>
       <c r="BH79" s="75"/>
       <c r="BI79" s="75"/>
       <c r="BJ79" s="75"/>
@@ -5702,11 +5534,7 @@
       <c r="BV79" s="75"/>
       <c r="BW79" s="75"/>
       <c r="BX79" s="75"/>
-      <c r="BY79" s="78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{task10_customer}}</t>
-        </is>
-      </c>
+      <c r="BY79" s="78"/>
       <c r="BZ79" s="78"/>
       <c r="CA79" s="78"/>
       <c r="CB79" s="78"/>

--- a/apps/api/templates/waybill-leg3.xlsx
+++ b/apps/api/templates/waybill-leg3.xlsx
@@ -314,7 +314,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="34">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -687,11 +687,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -941,6 +955,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2603,7 +2623,7 @@
     </row>
     <row r="37" spans="1:88" s="1" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.1">
       <c r="A37" s="11" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -2656,6 +2676,9 @@
       </c>
     </row>
     <row r="38" spans="1:88" s="1" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.1">
+      <c r="A38" s="11" t="s">
+        <v>39</v>
+      </c>
       <c r="BC38" s="31" t="s">
         <v>31</v>
       </c>
@@ -2683,33 +2706,33 @@
     </row>
     <row r="39" spans="1:88" s="1" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.1">
       <c r="A39" s="1"/>
-      <c r="Q39" s="33"/>
-      <c r="R39" s="33"/>
-      <c r="S39" s="33"/>
-      <c r="T39" s="33"/>
-      <c r="U39" s="33"/>
-      <c r="V39" s="33"/>
-      <c r="W39" s="33"/>
-      <c r="X39" s="33"/>
-      <c r="Y39" s="33"/>
-      <c r="AA39" s="34"/>
-      <c r="AB39" s="34"/>
-      <c r="AC39" s="34"/>
-      <c r="AD39" s="34"/>
-      <c r="AE39" s="34"/>
-      <c r="AF39" s="34"/>
-      <c r="AG39" s="34"/>
-      <c r="AH39" s="34"/>
-      <c r="AI39" s="34"/>
-      <c r="AJ39" s="34"/>
-      <c r="AK39" s="34"/>
-      <c r="AL39" s="34"/>
-      <c r="AM39" s="34"/>
-      <c r="AN39" s="34"/>
-      <c r="AO39" s="34"/>
-      <c r="AP39" s="34"/>
-      <c r="AQ39" s="34"/>
-      <c r="AR39" s="34"/>
+      <c r="Q39" s="84"/>
+      <c r="R39" s="84"/>
+      <c r="S39" s="84"/>
+      <c r="T39" s="84"/>
+      <c r="U39" s="84"/>
+      <c r="V39" s="84"/>
+      <c r="W39" s="84"/>
+      <c r="X39" s="84"/>
+      <c r="Y39" s="84"/>
+      <c r="AA39" s="85"/>
+      <c r="AB39" s="85"/>
+      <c r="AC39" s="85"/>
+      <c r="AD39" s="85"/>
+      <c r="AE39" s="85"/>
+      <c r="AF39" s="85"/>
+      <c r="AG39" s="85"/>
+      <c r="AH39" s="85"/>
+      <c r="AI39" s="85"/>
+      <c r="AJ39" s="85"/>
+      <c r="AK39" s="85"/>
+      <c r="AL39" s="85"/>
+      <c r="AM39" s="85"/>
+      <c r="AN39" s="85"/>
+      <c r="AO39" s="85"/>
+      <c r="AP39" s="85"/>
+      <c r="AQ39" s="85"/>
+      <c r="AR39" s="85"/>
       <c r="BC39" s="35"/>
       <c r="BD39" s="35"/>
       <c r="BE39" s="35"/>
@@ -2830,9 +2853,7 @@
       <c r="CJ41" s="39"/>
     </row>
     <row r="42" spans="1:88" s="1" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A42" s="11" t="s">
-        <v>37</v>
-      </c>
+      <c r="A42" s="11"/>
       <c r="B42" s="11"/>
       <c r="C42" s="11"/>
       <c r="D42" s="11"/>
@@ -2912,9 +2933,7 @@
       <c r="CJ42" s="41"/>
     </row>
     <row r="43" spans="1:88" s="1" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A43" s="11" t="s">
-        <v>39</v>
-      </c>
+      <c r="A43" s="11"/>
       <c r="B43" s="11"/>
       <c r="C43" s="11"/>
       <c r="D43" s="11"/>
@@ -3101,7 +3120,11 @@
       <c r="W48" s="33"/>
       <c r="X48" s="33"/>
       <c r="Y48" s="33"/>
-      <c r="AA48" s="34"/>
+      <c r="AA48" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{driver_short_name}}</t>
+        </is>
+      </c>
       <c r="AB48" s="34"/>
       <c r="AC48" s="34"/>
       <c r="AD48" s="34"/>
@@ -3403,7 +3426,11 @@
       <c r="W55" s="33"/>
       <c r="X55" s="33"/>
       <c r="Y55" s="33"/>
-      <c r="AA55" s="34"/>
+      <c r="AA55" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{driver_short_name}}</t>
+        </is>
+      </c>
       <c r="AB55" s="34"/>
       <c r="AC55" s="34"/>
       <c r="AD55" s="34"/>
@@ -6025,7 +6052,7 @@
     <row r="99" s="1" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.1"/>
     <row r="100" s="1" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.1"/>
   </sheetData>
-  <mergeCells count="222">
+  <mergeCells count="221">
     <mergeCell ref="A91:O91"/>
     <mergeCell ref="Q91:AE91"/>
     <mergeCell ref="AI91:BB91"/>
@@ -6200,7 +6227,6 @@
     <mergeCell ref="AK35:AR35"/>
     <mergeCell ref="AA36:AH36"/>
     <mergeCell ref="AK36:AR36"/>
-    <mergeCell ref="A37:AU37"/>
     <mergeCell ref="BC38:BJ38"/>
     <mergeCell ref="BK38:BV38"/>
     <mergeCell ref="Q39:Y39"/>
